--- a/04_DESIGN_TABLES/DesignTable_2403_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2403_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ35"/>
+  <dimension ref="A1:AQ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1084,11 +1084,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2403-04-04</t>
+          <t>2403-04-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="C5" t="n">
         <v>0.28868</v>
@@ -1139,61 +1139,61 @@
         <v>0.05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.21875</v>
+        <v>0.15625</v>
       </c>
       <c r="T5" t="n">
-        <v>0.075</v>
+        <v>0.063</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2608</v>
+        <v>0.19</v>
       </c>
       <c r="V5" t="n">
-        <v>0.182</v>
+        <v>0.125</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0795</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1135</v>
+        <v>0.1108</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4375</v>
+        <v>0.3125</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.05</v>
+        <v>0.04167</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.4538</v>
+        <v>0.367</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02706</v>
+        <v>0.02255</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0125</v>
+        <v>0.01042</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.05</v>
+        <v>0.04167</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.17</v>
+        <v>0.172</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.17</v>
+        <v>0.062</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.584</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2403-04-04</t>
+          <t>2403-04-02</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>Male Union, 7/16-20 x 7/16-20</t>
+          <t>Male Union, 7/16-20 x 5/16-24</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1208,56 +1208,56 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>7/16-20</t>
+          <t>5/16-24</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way ==MS51501 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L1@DRIVE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-04-02 col "L LGTH" = "1.270" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 200.4, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 33/33 rows with an Air-Way/OMi value agree with this catalog column to rounding; HEXB@HEX: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-04-02 col "C HEX" = "0.500" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 200.4, page verified) [Brennan = yes 2026-10-18] - body hex across flats; mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 33/33 rows with an Air-Way/OMi value agree with this catalog column to rounding; D1@BORE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-04-02 col "B1 DRILL" = "0.172" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 200.4, page verified) [Brennan = yes 2026-10-18] - bore at end A (first dash); mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 30/33 rows with an Air-Way/OMi value agree with this catalog column to rounding (3 differ, e.g. 2403-06-05 0.3 vs 0.234); D2@BORE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-04-02 col "B2 DRILL" = "0.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 200.4, page verified) [Brennan = yes 2026-10-18] - bore at end B (second dash); mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 32/33 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 2403-03-03 0.13 vs 1.25); THDMAJ_A@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; catalog B1 7/16-20; THDMAJ_B@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; catalog B2 5/16-24; JICA_RELIEFL@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JICA_THDZ@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JICA_CONEDIA@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JICA_LANDL@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JICA_SEATL@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); JICB_RELIEFL@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JICB_THDZ@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JICB_CONEDIA@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JICB_LANDL@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JICB_SEATL@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); RELIEFANG@DRIVE: gen_straight2 end_JICM constant 60 deg relief ramp (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; SEATB@DRIVE: gen_straight2 end_JICM constant 37 deg flare seat (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; $PRP@EndA_Thread: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text (format of the built 2403 rows); $PRP@EndB_Thread: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>MS51501 L1/hex/bore AGREE</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L1 / hex / D1 / D2 from the Brennan TFA catalog p5 alone (no OMi dimension, no Air-Way row); JIC ends from the end library</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>2403-04-04</t>
+          <t>2403-04-02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2403-05-04</t>
+          <t>2403-04-04</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1.37</v>
       </c>
       <c r="C6" t="n">
-        <v>0.32332</v>
+        <v>0.28868</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.25</v>
+        <v>0.21875</v>
       </c>
       <c r="F6" t="n">
         <v>0.075</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2606</v>
+        <v>0.2608</v>
       </c>
       <c r="H6" t="n">
-        <v>0.213</v>
+        <v>0.182</v>
       </c>
       <c r="I6" t="n">
         <v>0.0795</v>
@@ -1272,13 +1272,13 @@
         <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="N6" t="n">
         <v>0.05</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4536</v>
+        <v>0.4538</v>
       </c>
       <c r="P6" t="n">
         <v>0.02706</v>
@@ -1326,7 +1326,7 @@
         <v>0.05</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="AF6" t="n">
         <v>0.6850000000000001</v>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2403-05-04</t>
+          <t>2403-04-04</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>Male Union, 1/2-20 x 7/16-20</t>
+          <t>Male Union, 7/16-20 x 7/16-20</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>1/2-20</t>
+          <t>7/16-20</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1364,29 +1364,29 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
+          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way ==MS51501 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>unequal bores - bore step location unsourced</t>
+          <t>MS51501 L1/hex/bore AGREE</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>2403-05-04</t>
+          <t>2403-04-04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2403-05-05</t>
+          <t>2403-05-04</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1441,16 +1441,16 @@
         <v>0.05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.25</v>
+        <v>0.21875</v>
       </c>
       <c r="T7" t="n">
         <v>0.075</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2606</v>
+        <v>0.2608</v>
       </c>
       <c r="V7" t="n">
-        <v>0.213</v>
+        <v>0.182</v>
       </c>
       <c r="W7" t="n">
         <v>0.0795</v>
@@ -1459,13 +1459,13 @@
         <v>0.1135</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="Z7" t="n">
         <v>0.05</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4536</v>
+        <v>0.4538</v>
       </c>
       <c r="AB7" t="n">
         <v>0.02706</v>
@@ -1483,19 +1483,19 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="AH7" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2403-05-05</t>
+          <t>2403-05-04</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>Male Union, 1/2-20 x 1/2-20</t>
+          <t>Male Union, 1/2-20 x 7/16-20</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -1510,62 +1510,62 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>1/2-20</t>
+          <t>7/16-20</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way ==MS51501 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
+          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>MS51501 L1/hex/bore AGREE</t>
+          <t>unequal bores - bore step location unsourced</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>2403-05-05</t>
+          <t>2403-05-04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2403-06-04</t>
+          <t>2403-05-05</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="C8" t="n">
-        <v>0.36373</v>
+        <v>0.32332</v>
       </c>
       <c r="D8" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.28125</v>
+        <v>0.25</v>
       </c>
       <c r="F8" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2515</v>
+        <v>0.2606</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2405</v>
+        <v>0.213</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="K8" t="n">
         <v>60</v>
@@ -1574,34 +1574,34 @@
         <v>37</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4495</v>
+        <v>0.4536</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="R8" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.21875</v>
+        <v>0.25</v>
       </c>
       <c r="T8" t="n">
         <v>0.075</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2608</v>
+        <v>0.2606</v>
       </c>
       <c r="V8" t="n">
-        <v>0.182</v>
+        <v>0.213</v>
       </c>
       <c r="W8" t="n">
         <v>0.0795</v>
@@ -1610,13 +1610,13 @@
         <v>0.1135</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4375</v>
+        <v>0.5</v>
       </c>
       <c r="Z8" t="n">
         <v>0.05</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.4538</v>
+        <v>0.4536</v>
       </c>
       <c r="AB8" t="n">
         <v>0.02706</v>
@@ -1628,25 +1628,25 @@
         <v>0.05</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.703</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.697</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2403-06-04</t>
+          <t>2403-05-05</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>Male Union, 9/16-18 x 7/16-20</t>
+          <t>Male Union, 1/2-20 x 1/2-20</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -1656,39 +1656,39 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>9/16-18</t>
+          <t>1/2-20</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>7/16-20</t>
+          <t>1/2-20</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
+          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way ==MS51501 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>unequal bores - bore step location unsourced</t>
+          <t>MS51501 L1/hex/bore AGREE</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2403-06-04</t>
+          <t>2403-05-05</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2403-06-05</t>
+          <t>2403-06-04</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1743,16 +1743,16 @@
         <v>0.05556</v>
       </c>
       <c r="S9" t="n">
-        <v>0.25</v>
+        <v>0.21875</v>
       </c>
       <c r="T9" t="n">
         <v>0.075</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2606</v>
+        <v>0.2608</v>
       </c>
       <c r="V9" t="n">
-        <v>0.213</v>
+        <v>0.182</v>
       </c>
       <c r="W9" t="n">
         <v>0.0795</v>
@@ -1761,13 +1761,13 @@
         <v>0.1135</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="Z9" t="n">
         <v>0.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.4536</v>
+        <v>0.4538</v>
       </c>
       <c r="AB9" t="n">
         <v>0.02706</v>
@@ -1785,19 +1785,19 @@
         <v>0.703</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="AH9" t="n">
         <v>0.697</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2403-06-05</t>
+          <t>2403-06-04</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>Male Union, 9/16-18 x 1/2-20</t>
+          <t>Male Union, 9/16-18 x 7/16-20</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>1/2-20</t>
+          <t>7/16-20</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -1832,18 +1832,18 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2403-06-05</t>
+          <t>2403-06-04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2403-06-06</t>
+          <t>2403-06-05</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="C10" t="n">
         <v>0.36373</v>
@@ -1894,61 +1894,61 @@
         <v>0.05556</v>
       </c>
       <c r="S10" t="n">
-        <v>0.28125</v>
+        <v>0.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2515</v>
+        <v>0.2606</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2405</v>
+        <v>0.213</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.4495</v>
+        <v>0.4536</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AE10" t="n">
         <v>0.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.705</v>
+        <v>0.703</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.705</v>
+        <v>0.697</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2403-06-06</t>
+          <t>2403-06-05</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>Male Union, 9/16-18 x 9/16-18</t>
+          <t>Male Union, 9/16-18 x 1/2-20</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -1963,62 +1963,62 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>9/16-18</t>
+          <t>1/2-20</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way ==MS51501 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
+          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>MS51501 L1/hex/bore AGREE</t>
+          <t>unequal bores - bore step location unsourced</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2403-06-06</t>
+          <t>2403-06-05</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2403-08-04</t>
+          <t>2403-06-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="C11" t="n">
-        <v>0.46765</v>
+        <v>0.36373</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="E11" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="F11" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2837</v>
+        <v>0.2515</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3295</v>
+        <v>0.2405</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0984</v>
+        <v>0.0898</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="K11" t="n">
         <v>60</v>
@@ -2027,79 +2027,79 @@
         <v>37</v>
       </c>
       <c r="M11" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5367</v>
+        <v>0.4495</v>
       </c>
       <c r="P11" t="n">
-        <v>0.03383</v>
+        <v>0.03007</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01562</v>
+        <v>0.01389</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="S11" t="n">
-        <v>0.21875</v>
+        <v>0.28125</v>
       </c>
       <c r="T11" t="n">
-        <v>0.075</v>
+        <v>0.083</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2608</v>
+        <v>0.2515</v>
       </c>
       <c r="V11" t="n">
-        <v>0.182</v>
+        <v>0.2405</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0795</v>
+        <v>0.0898</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1135</v>
+        <v>0.1082</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4375</v>
+        <v>0.5625</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.05</v>
+        <v>0.05556</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.4538</v>
+        <v>0.4495</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.02706</v>
+        <v>0.03007</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.0125</v>
+        <v>0.01389</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.05</v>
+        <v>0.05556</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.8085</v>
+        <v>0.705</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.17</v>
+        <v>0.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.7015</v>
+        <v>0.705</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2403-08-04</t>
+          <t>2403-06-06</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>Male Union, 3/4-16 x 7/16-20</t>
+          <t>Male Union, 9/16-18 x 9/16-18</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2109,43 +2109,43 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>3/4-16</t>
+          <t>9/16-18</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>7/16-20</t>
+          <t>9/16-18</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
+          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way ==MS51501 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>unequal bores - bore step location unsourced</t>
+          <t>MS51501 L1/hex/bore AGREE</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2403-08-04</t>
+          <t>2403-06-06</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2403-08-06</t>
+          <t>2403-08-04</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="C12" t="n">
         <v>0.46765</v>
@@ -2196,61 +2196,61 @@
         <v>0.0625</v>
       </c>
       <c r="S12" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="T12" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="X12" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.4495</v>
+        <v>0.4538</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AE12" t="n">
         <v>0.39</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.8105</v>
+        <v>0.8085</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.7095</v>
+        <v>0.7015</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2403-08-06</t>
+          <t>2403-08-04</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>Male Union, 3/4-16 x 9/16-18</t>
+          <t>Male Union, 3/4-16 x 7/16-20</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>9/16-18</t>
+          <t>7/16-20</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -2285,39 +2285,39 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2403-08-06</t>
+          <t>2403-08-04</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2403-10-06</t>
+          <t>2403-08-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="C13" t="n">
-        <v>0.54271</v>
+        <v>0.46765</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="F13" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3553</v>
+        <v>0.2837</v>
       </c>
       <c r="H13" t="n">
-        <v>0.386</v>
+        <v>0.3295</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1114</v>
+        <v>0.0984</v>
       </c>
       <c r="J13" t="n">
         <v>0.1546</v>
@@ -2329,22 +2329,22 @@
         <v>37</v>
       </c>
       <c r="M13" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="N13" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6213</v>
+        <v>0.5367</v>
       </c>
       <c r="P13" t="n">
-        <v>0.03866</v>
+        <v>0.03383</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.01786</v>
+        <v>0.01562</v>
       </c>
       <c r="R13" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="S13" t="n">
         <v>0.28125</v>
@@ -2383,25 +2383,25 @@
         <v>0.05556</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.48</v>
+        <v>0.39</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.8105</v>
       </c>
       <c r="AG13" t="n">
         <v>0.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.739</v>
+        <v>0.7095</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2403-10-06</t>
+          <t>2403-08-06</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>Male Union, 7/8-14 x 9/16-18</t>
+          <t>Male Union, 3/4-16 x 9/16-18</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>7/8-14</t>
+          <t>3/4-16</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2436,24 +2436,24 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>2403-10-06</t>
+          <t>2403-08-06</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2403-10-08</t>
+          <t>2403-10-04</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="C14" t="n">
-        <v>0.54271</v>
+        <v>0.54098</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="E14" t="n">
         <v>0.4375</v>
@@ -2498,61 +2498,61 @@
         <v>0.07142999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>0.375</v>
+        <v>0.21875</v>
       </c>
       <c r="T14" t="n">
-        <v>0.094</v>
+        <v>0.075</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2837</v>
+        <v>0.2608</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3295</v>
+        <v>0.182</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0984</v>
+        <v>0.0795</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1546</v>
+        <v>0.1135</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.75</v>
+        <v>0.4375</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0625</v>
+        <v>0.05</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.5367</v>
+        <v>0.4538</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.03383</v>
+        <v>0.02706</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.01562</v>
+        <v>0.0125</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0625</v>
+        <v>0.05</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.48</v>
+        <v>0.484</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.9405</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.39</v>
+        <v>0.172</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.8395</v>
+        <v>0.731</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>2403-10-08</t>
+          <t>2403-10-04</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>Male Union, 7/8-14 x 3/4-16</t>
+          <t>Male Union, 7/8-14 x 7/16-20</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>3/4-16</t>
+          <t>7/16-20</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -2577,28 +2577,28 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L1@DRIVE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-10-04 col "L LGTH" = "1.67" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 321.4, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 33/33 rows with an Air-Way/OMi value agree with this catalog column to rounding; HEXB@HEX: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-10-04 col "C HEX" = "0.937" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 321.4, page verified) [Brennan = yes 2026-10-18] - body hex across flats; mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 33/33 rows with an Air-Way/OMi value agree with this catalog column to rounding; D1@BORE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-10-04 col "B1 DRILL" = "0.484" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 321.4, page verified) [Brennan = yes 2026-10-18] - bore at end A (first dash); mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 30/33 rows with an Air-Way/OMi value agree with this catalog column to rounding (3 differ, e.g. 2403-06-05 0.3 vs 0.234); D2@BORE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-10-04 col "B2 DRILL" = "0.172" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 321.4, page verified) [Brennan = yes 2026-10-18] - bore at end B (second dash); mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 32/33 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 2403-03-03 0.13 vs 1.25); THDMAJ_A@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; catalog B1 7/8-14; THDMAJ_B@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; catalog B2 7/16-20; JICA_RELIEFL@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JICA_THDZ@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JICA_CONEDIA@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JICA_LANDL@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JICA_SEATL@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); JICB_RELIEFL@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JICB_THDZ@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JICB_CONEDIA@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JICB_LANDL@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JICB_SEATL@DRIVE: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); RELIEFANG@DRIVE: gen_straight2 end_JICM constant 60 deg relief ramp (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; SEATB@DRIVE: gen_straight2 end_JICM constant 37 deg flare seat (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; $PRP@EndA_Thread: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text (format of the built 2403 rows); $PRP@EndB_Thread: end library gen_straight2 JIC[4] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>unequal bores - bore step location unsourced</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L1 / hex / D1 / D2 from the Brennan TFA catalog p5 alone (no OMi dimension, no Air-Way row); JIC ends from the end library</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>2403-10-08</t>
+          <t>2403-10-04</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2403-10-10</t>
+          <t>2403-10-06</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="C15" t="n">
         <v>0.54271</v>
@@ -2649,61 +2649,61 @@
         <v>0.07142999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="T15" t="n">
-        <v>0.107</v>
+        <v>0.083</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3553</v>
+        <v>0.2515</v>
       </c>
       <c r="V15" t="n">
-        <v>0.386</v>
+        <v>0.2405</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1114</v>
+        <v>0.0898</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.875</v>
+        <v>0.5625</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.6213</v>
+        <v>0.4495</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.03866</v>
+        <v>0.03007</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.01786</v>
+        <v>0.01389</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AE15" t="n">
         <v>0.48</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.739</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>2403-10-10</t>
+          <t>2403-10-06</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>Male Union, 7/8-14 x 7/8-14</t>
+          <t>Male Union, 7/8-14 x 9/16-18</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -2718,62 +2718,62 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>7/8-14</t>
+          <t>9/16-18</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way ==MS51501 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
+          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>MS51501 L1/hex/bore AGREE</t>
+          <t>unequal bores - bore step location unsourced</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>2403-10-10</t>
+          <t>2403-10-06</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2403-12-06</t>
+          <t>2403-10-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="C16" t="n">
-        <v>0.65241</v>
+        <v>0.54271</v>
       </c>
       <c r="D16" t="n">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="F16" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4715</v>
+        <v>0.386</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1299</v>
+        <v>0.1114</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="K16" t="n">
         <v>60</v>
@@ -2782,79 +2782,79 @@
         <v>37</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="N16" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7045</v>
+        <v>0.6213</v>
       </c>
       <c r="P16" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="R16" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>0.28125</v>
+        <v>0.375</v>
       </c>
       <c r="T16" t="n">
-        <v>0.083</v>
+        <v>0.094</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2515</v>
+        <v>0.2837</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2405</v>
+        <v>0.3295</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0898</v>
+        <v>0.0984</v>
       </c>
       <c r="X16" t="n">
-        <v>0.1082</v>
+        <v>0.1546</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.5625</v>
+        <v>0.75</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.05556</v>
+        <v>0.0625</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.4495</v>
+        <v>0.5367</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.03007</v>
+        <v>0.03383</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.01389</v>
+        <v>0.01562</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.05556</v>
+        <v>0.0625</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.079</v>
+        <v>0.9405</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.771</v>
+        <v>0.8395</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2403-12-06</t>
+          <t>2403-10-08</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>Male Union, 1 1/16-12 x 9/16-18</t>
+          <t>Male Union, 7/8-14 x 3/4-16</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>1 1/16-12</t>
+          <t>7/8-14</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>9/16-18</t>
+          <t>3/4-16</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -2889,42 +2889,42 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>2403-12-06</t>
+          <t>2403-10-08</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2403-12-08</t>
+          <t>2403-10-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="C17" t="n">
-        <v>0.65241</v>
+        <v>0.54271</v>
       </c>
       <c r="D17" t="n">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="F17" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4715</v>
+        <v>0.386</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1299</v>
+        <v>0.1114</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="K17" t="n">
         <v>60</v>
@@ -2933,79 +2933,79 @@
         <v>37</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="N17" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7045</v>
+        <v>0.6213</v>
       </c>
       <c r="P17" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="R17" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="T17" t="n">
-        <v>0.094</v>
+        <v>0.107</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2837</v>
+        <v>0.3553</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3295</v>
+        <v>0.386</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0984</v>
+        <v>0.1114</v>
       </c>
       <c r="X17" t="n">
         <v>0.1546</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.0625</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.5367</v>
+        <v>0.6213</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.03383</v>
+        <v>0.03866</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.01562</v>
+        <v>0.01786</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0625</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.0785</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.39</v>
+        <v>0.48</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.8715000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>2403-12-08</t>
+          <t>2403-10-10</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>Male Union, 1 1/16-12 x 3/4-16</t>
+          <t>Male Union, 7/8-14 x 7/8-14</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -3015,43 +3015,43 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>1 1/16-12</t>
+          <t>7/8-14</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>3/4-16</t>
+          <t>7/8-14</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
+          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way ==MS51501 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>unequal bores - bore step location unsourced</t>
+          <t>MS51501 L1/hex/bore AGREE</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>2403-12-08</t>
+          <t>2403-10-10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2403-12-10</t>
+          <t>2403-12-06</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="C18" t="n">
         <v>0.65241</v>
@@ -3102,61 +3102,61 @@
         <v>0.08333</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="T18" t="n">
-        <v>0.107</v>
+        <v>0.083</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3553</v>
+        <v>0.2515</v>
       </c>
       <c r="V18" t="n">
-        <v>0.386</v>
+        <v>0.2405</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1114</v>
+        <v>0.0898</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.875</v>
+        <v>0.5625</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.6213</v>
+        <v>0.4495</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.03866</v>
+        <v>0.03007</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.01786</v>
+        <v>0.01389</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AE18" t="n">
         <v>0.61</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.078</v>
+        <v>1.079</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.972</v>
+        <v>0.771</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2403-12-10</t>
+          <t>2403-12-06</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>Male Union, 1 1/16-12 x 7/8-14</t>
+          <t>Male Union, 1 1/16-12 x 9/16-18</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>7/8-14</t>
+          <t>9/16-18</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -3191,18 +3191,18 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>2403-12-10</t>
+          <t>2403-12-06</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2403-12-12</t>
+          <t>2403-12-08</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="C19" t="n">
         <v>0.65241</v>
@@ -3253,61 +3253,61 @@
         <v>0.08333</v>
       </c>
       <c r="S19" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="T19" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3895</v>
+        <v>0.2837</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4715</v>
+        <v>0.3295</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1299</v>
+        <v>0.0984</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.0625</v>
+        <v>0.75</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.7045</v>
+        <v>0.5367</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.04511</v>
+        <v>0.03383</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.02083</v>
+        <v>0.01562</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AE19" t="n">
         <v>0.61</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.08</v>
+        <v>1.0785</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.61</v>
+        <v>0.39</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.08</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2403-12-12</t>
+          <t>2403-12-08</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>Male Union, 1 1/16-12 x 1 1/16-12</t>
+          <t>Male Union, 1 1/16-12 x 3/4-16</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -3322,62 +3322,62 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>1 1/16-12</t>
+          <t>3/4-16</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way ==MS51501 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
+          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>MS51501 L1/hex/bore AGREE</t>
+          <t>unequal bores - bore step location unsourced</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>2403-12-12</t>
+          <t>2403-12-08</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2403-16-08</t>
+          <t>2403-12-10</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="C20" t="n">
-        <v>0.79674</v>
+        <v>0.65241</v>
       </c>
       <c r="D20" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="E20" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="F20" t="n">
         <v>0.125</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="K20" t="n">
         <v>60</v>
@@ -3386,13 +3386,13 @@
         <v>37</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="N20" t="n">
         <v>0.08333</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7045</v>
       </c>
       <c r="P20" t="n">
         <v>0.04511</v>
@@ -3404,61 +3404,61 @@
         <v>0.08333</v>
       </c>
       <c r="S20" t="n">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="T20" t="n">
-        <v>0.094</v>
+        <v>0.107</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2837</v>
+        <v>0.3553</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3295</v>
+        <v>0.386</v>
       </c>
       <c r="W20" t="n">
-        <v>0.0984</v>
+        <v>0.1114</v>
       </c>
       <c r="X20" t="n">
         <v>0.1546</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.0625</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.5367</v>
+        <v>0.6213</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.03383</v>
+        <v>0.03866</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.01562</v>
+        <v>0.01786</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.0625</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.127</v>
+        <v>1.078</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.39</v>
+        <v>0.48</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.873</v>
+        <v>0.972</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2403-16-08</t>
+          <t>2403-12-10</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>Male Union, 1 5/16-12 x 3/4-16</t>
+          <t>Male Union, 1 1/16-12 x 7/8-14</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>1 5/16-12</t>
+          <t>1 1/16-12</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>3/4-16</t>
+          <t>7/8-14</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
@@ -3493,42 +3493,42 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>2403-16-08</t>
+          <t>2403-12-10</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2403-16-12</t>
+          <t>2403-12-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="C21" t="n">
-        <v>0.79674</v>
+        <v>0.65241</v>
       </c>
       <c r="D21" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="E21" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="F21" t="n">
         <v>0.125</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="K21" t="n">
         <v>60</v>
@@ -3537,13 +3537,13 @@
         <v>37</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="N21" t="n">
         <v>0.08333</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7045</v>
       </c>
       <c r="P21" t="n">
         <v>0.04511</v>
@@ -3591,25 +3591,25 @@
         <v>0.08333</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.1235</v>
+        <v>1.08</v>
       </c>
       <c r="AG21" t="n">
         <v>0.61</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.0765</v>
+        <v>1.08</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2403-16-12</t>
+          <t>2403-12-12</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>Male Union, 1 5/16-12 x 1 1/16-12</t>
+          <t>Male Union, 1 1/16-12 x 1 1/16-12</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>1 5/16-12</t>
+          <t>1 1/16-12</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -3629,33 +3629,33 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
+          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way ==MS51501 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>unequal bores - bore step location unsourced</t>
+          <t>MS51501 L1/hex/bore AGREE</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>2403-16-12</t>
+          <t>2403-12-12</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2403-16-16</t>
+          <t>2403-16-08</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
         <v>0.79674</v>
@@ -3706,61 +3706,61 @@
         <v>0.08333</v>
       </c>
       <c r="S22" t="n">
-        <v>0.65625</v>
+        <v>0.375</v>
       </c>
       <c r="T22" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4365</v>
+        <v>0.2837</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5965</v>
+        <v>0.3295</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1292</v>
+        <v>0.0984</v>
       </c>
       <c r="X22" t="n">
-        <v>0.1858</v>
+        <v>0.1546</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3125</v>
+        <v>0.75</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.5367</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.04511</v>
+        <v>0.03383</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.02083</v>
+        <v>0.01562</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AE22" t="n">
         <v>0.84</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.125</v>
+        <v>1.127</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.84</v>
+        <v>0.39</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.125</v>
+        <v>0.873</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2403-16-16</t>
+          <t>2403-16-08</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>Male Union, 1 5/16-12 x 1 5/16-12</t>
+          <t>Male Union, 1 5/16-12 x 3/4-16</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -3775,62 +3775,62 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>1 5/16-12</t>
+          <t>3/4-16</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way ==MS51501 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
+          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>MS51501 L1/hex/bore AGREE</t>
+          <t>unequal bores - bore step location unsourced</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>2403-16-16</t>
+          <t>2403-16-08</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2403-20-12</t>
+          <t>2403-16-10</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.97572</v>
+        <v>0.79386</v>
       </c>
       <c r="D23" t="n">
-        <v>1.69</v>
+        <v>1.375</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="F23" t="n">
         <v>0.125</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="H23" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="K23" t="n">
         <v>60</v>
@@ -3839,13 +3839,13 @@
         <v>37</v>
       </c>
       <c r="M23" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="N23" t="n">
         <v>0.08333</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7986</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="P23" t="n">
         <v>0.04511</v>
@@ -3857,61 +3857,61 @@
         <v>0.08333</v>
       </c>
       <c r="S23" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="T23" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="V23" t="n">
-        <v>0.4715</v>
+        <v>0.386</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1299</v>
+        <v>0.1114</v>
       </c>
       <c r="X23" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.7045</v>
+        <v>0.6213</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.08</v>
+        <v>0.844</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.217</v>
+        <v>1.1265</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.61</v>
+        <v>0.484</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.123</v>
+        <v>0.9735</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2403-20-12</t>
+          <t>2403-16-10</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>Male Union, 1 5/8-12 x 1 1/16-12</t>
+          <t>Male Union, 1 5/16-12 x 7/8-14</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>1 5/8-12</t>
+          <t>1 5/16-12</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>1 1/16-12</t>
+          <t>7/8-14</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -3936,52 +3936,52 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L1@DRIVE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-16-10 col "L LGTH" = "2.10" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 472.6, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 33/33 rows with an Air-Way/OMi value agree with this catalog column to rounding; HEXB@HEX: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-16-10 col "C HEX" = "1.375" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 472.6, page verified) [Brennan = yes 2026-10-18] - body hex across flats; mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 33/33 rows with an Air-Way/OMi value agree with this catalog column to rounding; D1@BORE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-16-10 col "B1 DRILL" = "0.844" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 472.6, page verified) [Brennan = yes 2026-10-18] - bore at end A (first dash); mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 30/33 rows with an Air-Way/OMi value agree with this catalog column to rounding (3 differ, e.g. 2403-06-05 0.3 vs 0.234); D2@BORE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-16-10 col "B2 DRILL" = "0.484" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 472.6, page verified) [Brennan = yes 2026-10-18] - bore at end B (second dash); mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 32/33 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 2403-03-03 0.13 vs 1.25); THDMAJ_A@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; catalog B1 1 5/16-12; THDMAJ_B@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; catalog B2 7/8-14; JICA_RELIEFL@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JICA_THDZ@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JICA_CONEDIA@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JICA_LANDL@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JICA_SEATL@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); JICB_RELIEFL@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JICB_THDZ@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JICB_CONEDIA@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JICB_LANDL@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JICB_SEATL@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); RELIEFANG@DRIVE: gen_straight2 end_JICM constant 60 deg relief ramp (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; SEATB@DRIVE: gen_straight2 end_JICM constant 37 deg flare seat (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; $PRP@EndA_Thread: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text (format of the built 2403 rows); $PRP@EndB_Thread: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>unequal bores - bore step location unsourced</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L1 / hex / D1 / D2 from the Brennan TFA catalog p5 alone (no OMi dimension, no Air-Way row); JIC ends from the end library</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>2403-20-12</t>
+          <t>2403-16-10</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2403-20-20</t>
+          <t>2403-16-12</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="C24" t="n">
-        <v>0.97572</v>
+        <v>0.79674</v>
       </c>
       <c r="D24" t="n">
-        <v>1.69</v>
+        <v>1.38</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="F24" t="n">
         <v>0.125</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="H24" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="K24" t="n">
         <v>60</v>
@@ -3990,13 +3990,13 @@
         <v>37</v>
       </c>
       <c r="M24" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="N24" t="n">
         <v>0.08333</v>
       </c>
       <c r="O24" t="n">
-        <v>0.7986</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="P24" t="n">
         <v>0.04511</v>
@@ -4008,31 +4008,31 @@
         <v>0.08333</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="T24" t="n">
         <v>0.125</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4316</v>
+        <v>0.3895</v>
       </c>
       <c r="V24" t="n">
-        <v>0.753</v>
+        <v>0.4715</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1288</v>
+        <v>0.1299</v>
       </c>
       <c r="X24" t="n">
-        <v>0.2382</v>
+        <v>0.1851</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.625</v>
+        <v>1.0625</v>
       </c>
       <c r="Z24" t="n">
         <v>0.08333</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.7986</v>
+        <v>0.7045</v>
       </c>
       <c r="AB24" t="n">
         <v>0.04511</v>
@@ -4044,25 +4044,25 @@
         <v>0.08333</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.215</v>
+        <v>1.1235</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.08</v>
+        <v>0.61</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.215</v>
+        <v>1.0765</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>2403-20-20</t>
+          <t>2403-16-12</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>Male Union, 1 5/8-12 x 1 5/8-12</t>
+          <t>Male Union, 1 5/16-12 x 1 1/16-12</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -4072,67 +4072,67 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>1 5/8-12</t>
+          <t>1 5/16-12</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>1 5/8-12</t>
+          <t>1 1/16-12</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way ==MS51501 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
+          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>MS51501 L1/hex/bore AGREE</t>
+          <t>unequal bores - bore step location unsourced</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>2403-20-20</t>
+          <t>2403-16-12</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2403-24-20</t>
+          <t>2403-16-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="C25" t="n">
-        <v>1.1547</v>
+        <v>0.79674</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="F25" t="n">
         <v>0.125</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5454</v>
+        <v>0.4365</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.5965</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1298</v>
+        <v>0.1292</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2482</v>
+        <v>0.1858</v>
       </c>
       <c r="K25" t="n">
         <v>60</v>
@@ -4141,13 +4141,13 @@
         <v>37</v>
       </c>
       <c r="M25" t="n">
-        <v>1.875</v>
+        <v>1.3125</v>
       </c>
       <c r="N25" t="n">
         <v>0.08333</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9234</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="P25" t="n">
         <v>0.04511</v>
@@ -4159,31 +4159,31 @@
         <v>0.08333</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="T25" t="n">
         <v>0.125</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="V25" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="X25" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="Z25" t="n">
         <v>0.08333</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.7986</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="AB25" t="n">
         <v>0.04511</v>
@@ -4195,25 +4195,25 @@
         <v>0.08333</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.31</v>
+        <v>0.84</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.3725</v>
+        <v>1.125</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.2475</v>
+        <v>1.125</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>2403-24-20</t>
+          <t>2403-16-16</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>Male Union, 1 7/8-12 x 1 5/8-12</t>
+          <t>Male Union, 1 5/16-12 x 1 5/16-12</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -4223,67 +4223,67 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>1 7/8-12</t>
+          <t>1 5/16-12</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>1 5/8-12</t>
+          <t>1 5/16-12</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
+          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way ==MS51501 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>unequal bores - bore step location unsourced</t>
+          <t>MS51501 L1/hex/bore AGREE</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>2403-24-20</t>
+          <t>2403-16-16</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2403-24-24</t>
+          <t>2403-20-12</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="C26" t="n">
-        <v>1.1547</v>
+        <v>0.97572</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="F26" t="n">
         <v>0.125</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5454</v>
+        <v>0.4316</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1298</v>
+        <v>0.1288</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2482</v>
+        <v>0.2382</v>
       </c>
       <c r="K26" t="n">
         <v>60</v>
@@ -4292,13 +4292,13 @@
         <v>37</v>
       </c>
       <c r="M26" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="N26" t="n">
         <v>0.08333</v>
       </c>
       <c r="O26" t="n">
-        <v>0.9234</v>
+        <v>0.7986</v>
       </c>
       <c r="P26" t="n">
         <v>0.04511</v>
@@ -4310,31 +4310,31 @@
         <v>0.08333</v>
       </c>
       <c r="S26" t="n">
-        <v>0.9375</v>
+        <v>0.53125</v>
       </c>
       <c r="T26" t="n">
         <v>0.125</v>
       </c>
       <c r="U26" t="n">
-        <v>0.5454</v>
+        <v>0.3895</v>
       </c>
       <c r="V26" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.4715</v>
       </c>
       <c r="W26" t="n">
-        <v>0.1298</v>
+        <v>0.1299</v>
       </c>
       <c r="X26" t="n">
-        <v>0.2482</v>
+        <v>0.1851</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.875</v>
+        <v>1.0625</v>
       </c>
       <c r="Z26" t="n">
         <v>0.08333</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.9234</v>
+        <v>0.7045</v>
       </c>
       <c r="AB26" t="n">
         <v>0.04511</v>
@@ -4346,25 +4346,25 @@
         <v>0.08333</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.375</v>
+        <v>1.217</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.31</v>
+        <v>0.61</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.375</v>
+        <v>1.123</v>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>2403-24-24</t>
+          <t>2403-20-12</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>Male Union, 1 7/8-12 x 1 7/8-12</t>
+          <t>Male Union, 1 5/8-12 x 1 1/16-12</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -4374,67 +4374,67 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>1 7/8-12</t>
+          <t>1 5/8-12</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>1 7/8-12</t>
+          <t>1 1/16-12</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way ==MS51501 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
+          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>MS51501 L1/hex/bore AGREE</t>
+          <t>unequal bores - bore step location unsourced</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>2403-24-24</t>
+          <t>2403-20-12</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2403-32-24</t>
+          <t>2403-20-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.15</v>
+        <v>2.38</v>
       </c>
       <c r="C27" t="n">
-        <v>1.51843</v>
+        <v>0.97572</v>
       </c>
       <c r="D27" t="n">
-        <v>2.63</v>
+        <v>1.69</v>
       </c>
       <c r="E27" t="n">
-        <v>1.25</v>
+        <v>0.8125</v>
       </c>
       <c r="F27" t="n">
         <v>0.125</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7124</v>
+        <v>0.4316</v>
       </c>
       <c r="H27" t="n">
-        <v>1.19</v>
+        <v>0.753</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1292</v>
+        <v>0.1288</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3318</v>
+        <v>0.2382</v>
       </c>
       <c r="K27" t="n">
         <v>60</v>
@@ -4443,13 +4443,13 @@
         <v>37</v>
       </c>
       <c r="M27" t="n">
-        <v>2.5</v>
+        <v>1.625</v>
       </c>
       <c r="N27" t="n">
         <v>0.08333</v>
       </c>
       <c r="O27" t="n">
-        <v>1.1734</v>
+        <v>0.7986</v>
       </c>
       <c r="P27" t="n">
         <v>0.04511</v>
@@ -4461,31 +4461,31 @@
         <v>0.08333</v>
       </c>
       <c r="S27" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="T27" t="n">
         <v>0.125</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5454</v>
+        <v>0.4365</v>
       </c>
       <c r="V27" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.5965</v>
       </c>
       <c r="W27" t="n">
-        <v>0.1298</v>
+        <v>0.1292</v>
       </c>
       <c r="X27" t="n">
-        <v>0.2482</v>
+        <v>0.1858</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.875</v>
+        <v>1.3125</v>
       </c>
       <c r="Z27" t="n">
         <v>0.08333</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.9234</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="AB27" t="n">
         <v>0.04511</v>
@@ -4497,25 +4497,25 @@
         <v>0.08333</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.78</v>
+        <v>1.08</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.7</v>
+        <v>1.2135</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.31</v>
+        <v>0.84</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.45</v>
+        <v>1.1665</v>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>2403-32-24</t>
+          <t>2403-20-16</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>Male Union, 2 1/2-12 x 1 7/8-12</t>
+          <t>Male Union, 1 5/8-12 x 1 5/16-12</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -4525,17 +4525,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2 1/2-12</t>
+          <t>1 5/8-12</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>1 7/8-12</t>
+          <t>1 5/16-12</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -4545,47 +4545,47 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>unequal bores - bore step location unsourced</t>
+          <t>unequal bores - bore step location unsourced | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p005-t01: agrees on L1@DRIVE, HEXB@HEX, D1@BORE, D2@BORE</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>2403-32-24</t>
+          <t>2403-20-16</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2403-32-32</t>
+          <t>2403-20-20</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.4</v>
+        <v>2.43</v>
       </c>
       <c r="C28" t="n">
-        <v>1.51843</v>
+        <v>0.97572</v>
       </c>
       <c r="D28" t="n">
-        <v>2.63</v>
+        <v>1.69</v>
       </c>
       <c r="E28" t="n">
-        <v>1.25</v>
+        <v>0.8125</v>
       </c>
       <c r="F28" t="n">
         <v>0.125</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7124</v>
+        <v>0.4316</v>
       </c>
       <c r="H28" t="n">
-        <v>1.19</v>
+        <v>0.753</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1292</v>
+        <v>0.1288</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3318</v>
+        <v>0.2382</v>
       </c>
       <c r="K28" t="n">
         <v>60</v>
@@ -4594,13 +4594,13 @@
         <v>37</v>
       </c>
       <c r="M28" t="n">
-        <v>2.5</v>
+        <v>1.625</v>
       </c>
       <c r="N28" t="n">
         <v>0.08333</v>
       </c>
       <c r="O28" t="n">
-        <v>1.1734</v>
+        <v>0.7986</v>
       </c>
       <c r="P28" t="n">
         <v>0.04511</v>
@@ -4612,31 +4612,31 @@
         <v>0.08333</v>
       </c>
       <c r="S28" t="n">
-        <v>1.25</v>
+        <v>0.8125</v>
       </c>
       <c r="T28" t="n">
         <v>0.125</v>
       </c>
       <c r="U28" t="n">
-        <v>0.7124</v>
+        <v>0.4316</v>
       </c>
       <c r="V28" t="n">
-        <v>1.19</v>
+        <v>0.753</v>
       </c>
       <c r="W28" t="n">
-        <v>0.1292</v>
+        <v>0.1288</v>
       </c>
       <c r="X28" t="n">
-        <v>0.3318</v>
+        <v>0.2382</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.5</v>
+        <v>1.625</v>
       </c>
       <c r="Z28" t="n">
         <v>0.08333</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.1734</v>
+        <v>0.7986</v>
       </c>
       <c r="AB28" t="n">
         <v>0.04511</v>
@@ -4648,25 +4648,25 @@
         <v>0.08333</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.78</v>
+        <v>1.08</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.7</v>
+        <v>1.215</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.78</v>
+        <v>1.08</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.7</v>
+        <v>1.215</v>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>2403-32-32</t>
+          <t>2403-20-20</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>Male Union, 2 1/2-12 x 2 1/2-12</t>
+          <t>Male Union, 1 5/8-12 x 1 5/8-12</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2 1/2-12</t>
+          <t>1 5/8-12</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>2 1/2-12</t>
+          <t>1 5/8-12</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
@@ -4701,42 +4701,42 @@
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>2403-32-32</t>
+          <t>2403-20-20</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2403-LH-04-04</t>
+          <t>2403-24-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.37</v>
+        <v>2.58</v>
       </c>
       <c r="C29" t="n">
-        <v>0.39837</v>
+        <v>1.1547</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6899999999999999</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>0.21875</v>
+        <v>0.9375</v>
       </c>
       <c r="F29" t="n">
-        <v>0.075</v>
+        <v>0.125</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2608</v>
+        <v>0.5454</v>
       </c>
       <c r="H29" t="n">
-        <v>0.182</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0795</v>
+        <v>0.1298</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1135</v>
+        <v>0.2482</v>
       </c>
       <c r="K29" t="n">
         <v>60</v>
@@ -4745,79 +4745,79 @@
         <v>37</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4375</v>
+        <v>1.875</v>
       </c>
       <c r="N29" t="n">
-        <v>0.05</v>
+        <v>0.08333</v>
       </c>
       <c r="O29" t="n">
-        <v>0.4538</v>
+        <v>0.9234</v>
       </c>
       <c r="P29" t="n">
-        <v>0.02706</v>
+        <v>0.04511</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0125</v>
+        <v>0.02083</v>
       </c>
       <c r="R29" t="n">
-        <v>0.05</v>
+        <v>0.08333</v>
       </c>
       <c r="S29" t="n">
-        <v>0.21875</v>
+        <v>0.65625</v>
       </c>
       <c r="T29" t="n">
-        <v>0.075</v>
+        <v>0.125</v>
       </c>
       <c r="U29" t="n">
-        <v>0.2608</v>
+        <v>0.4365</v>
       </c>
       <c r="V29" t="n">
-        <v>0.182</v>
+        <v>0.5965</v>
       </c>
       <c r="W29" t="n">
-        <v>0.0795</v>
+        <v>0.1292</v>
       </c>
       <c r="X29" t="n">
-        <v>0.1135</v>
+        <v>0.1858</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.4375</v>
+        <v>1.3125</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.05</v>
+        <v>0.08333</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.4538</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.02706</v>
+        <v>0.04511</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.0125</v>
+        <v>0.02083</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.05</v>
+        <v>0.08333</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.17</v>
+        <v>1.312</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.6850000000000001</v>
+        <v>1.376</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.17</v>
+        <v>0.844</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.6850000000000001</v>
+        <v>1.204</v>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>2403-LH-04-04</t>
+          <t>2403-24-16</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>Male Union Large Hex, 7/16-20 x 7/16-20</t>
+          <t>Male Union, 1 7/8-12 x 1 5/16-12</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>7/16-20</t>
+          <t>1 7/8-12</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>7/16-20</t>
+          <t>1 5/16-12</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
@@ -4842,47 +4842,52 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Air-Way s63 only (double-pass 16 rows); JIC male end axials VERIFIED lib-wide (MS33656J); large-hex variant of 2403 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled; 2403-LH = the LARGE-HEX union (OMi "Straight-Large Hex", Air-Way s63, review table DesignTable_2403LH.xlsx), folded into the 2403 master as rows of the same shape: same JIC ends per dash, L1 and bores D1 / D2 from the 2403-LH table, hex = its C2 (as the legacy 2403 builder already did, 2026-09-06)</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L1@DRIVE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-24-16 col "L LGTH" = "2.580" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 553.2, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 33/33 rows with an Air-Way/OMi value agree with this catalog column to rounding; HEXB@HEX: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-24-16 col "C HEX" = "2.000" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 553.2, page verified) [Brennan = yes 2026-10-18] - body hex across flats; mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 33/33 rows with an Air-Way/OMi value agree with this catalog column to rounding; D1@BORE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-24-16 col "B1 DRILL" = "1.312" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 553.2, page verified) [Brennan = yes 2026-10-18] - bore at end A (first dash); mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 30/33 rows with an Air-Way/OMi value agree with this catalog column to rounding (3 differ, e.g. 2403-06-05 0.3 vs 0.234); D2@BORE: Brennan TFA catalog p5 table TFA-p005-t01 "2403 MJ-MJ STRAIGHT" row 2403-24-16 col "B2 DRILL" = "0.844" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 553.2, page verified) [Brennan = yes 2026-10-18] - bore at end B (second dash); mapping: TFA p5 2403 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bore at end B1/B2 (impact/F2a.json, pairing certain); same-table check on today's base: 32/33 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 2403-03-03 0.13 vs 1.25); THDMAJ_A@DRIVE: end library gen_straight2 JIC[24] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; catalog B1 1-7/8-12; THDMAJ_B@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; catalog B2 1-5/16-12; JICA_RELIEFL@DRIVE: end library gen_straight2 JIC[24] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JICA_THDZ@DRIVE: end library gen_straight2 JIC[24] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JICA_CONEDIA@DRIVE: end library gen_straight2 JIC[24] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JICA_LANDL@DRIVE: end library gen_straight2 JIC[24] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JICA_SEATL@DRIVE: end library gen_straight2 JIC[24] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); JICB_RELIEFL@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JICB_THDZ@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JICB_CONEDIA@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JICB_LANDL@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JICB_SEATL@DRIVE: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); RELIEFANG@DRIVE: gen_straight2 end_JICM constant 60 deg relief ramp (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; SEATB@DRIVE: gen_straight2 end_JICM constant 37 deg flare seat (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; $PRP@EndA_Thread: end library gen_straight2 JIC[24] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text (format of the built 2403 rows); $PRP@EndB_Thread: end library gen_straight2 JIC[16] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L1 / hex / D1 / D2 from the Brennan TFA catalog p5 alone (no OMi dimension, no Air-Way row); JIC ends from the end library</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>2403-LH-04-04</t>
+          <t>2403-24-16</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2403-LH-06-06</t>
+          <t>2403-24-20</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.41</v>
+        <v>2.62</v>
       </c>
       <c r="C30" t="n">
-        <v>0.46765</v>
+        <v>1.1547</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8100000000000001</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>0.28125</v>
+        <v>0.9375</v>
       </c>
       <c r="F30" t="n">
-        <v>0.083</v>
+        <v>0.125</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2515</v>
+        <v>0.5454</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2405</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0898</v>
+        <v>0.1298</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1082</v>
+        <v>0.2482</v>
       </c>
       <c r="K30" t="n">
         <v>60</v>
@@ -4891,79 +4896,79 @@
         <v>37</v>
       </c>
       <c r="M30" t="n">
-        <v>0.5625</v>
+        <v>1.875</v>
       </c>
       <c r="N30" t="n">
-        <v>0.05556</v>
+        <v>0.08333</v>
       </c>
       <c r="O30" t="n">
-        <v>0.4495</v>
+        <v>0.9234</v>
       </c>
       <c r="P30" t="n">
-        <v>0.03007</v>
+        <v>0.04511</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.01389</v>
+        <v>0.02083</v>
       </c>
       <c r="R30" t="n">
-        <v>0.05556</v>
+        <v>0.08333</v>
       </c>
       <c r="S30" t="n">
-        <v>0.28125</v>
+        <v>0.8125</v>
       </c>
       <c r="T30" t="n">
-        <v>0.083</v>
+        <v>0.125</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2515</v>
+        <v>0.4316</v>
       </c>
       <c r="V30" t="n">
-        <v>0.2405</v>
+        <v>0.753</v>
       </c>
       <c r="W30" t="n">
-        <v>0.0898</v>
+        <v>0.1288</v>
       </c>
       <c r="X30" t="n">
-        <v>0.1082</v>
+        <v>0.2382</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.5625</v>
+        <v>1.625</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.05556</v>
+        <v>0.08333</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.4495</v>
+        <v>0.7986</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.03007</v>
+        <v>0.04511</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.01389</v>
+        <v>0.02083</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.05556</v>
+        <v>0.08333</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.705</v>
+        <v>1.3725</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.3</v>
+        <v>1.08</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.705</v>
+        <v>1.2475</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>2403-LH-06-06</t>
+          <t>2403-24-20</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>Male Union Large Hex, 9/16-18 x 9/16-18</t>
+          <t>Male Union, 1 7/8-12 x 1 5/8-12</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -4973,12 +4978,12 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>9/16-18</t>
+          <t>1 7/8-12</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>9/16-18</t>
+          <t>1 5/8-12</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
@@ -4988,47 +4993,52 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Air-Way s63 only (double-pass 16 rows); JIC male end axials VERIFIED lib-wide (MS33656J); large-hex variant of 2403 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled; 2403-LH = the LARGE-HEX union (OMi "Straight-Large Hex", Air-Way s63, review table DesignTable_2403LH.xlsx), folded into the 2403 master as rows of the same shape: same JIC ends per dash, L1 and bores D1 / D2 from the 2403-LH table, hex = its C2 (as the legacy 2403 builder already did, 2026-09-06)</t>
+          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>unequal bores - bore step location unsourced</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>2403-LH-06-06</t>
+          <t>2403-24-20</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2403-LH-08-08</t>
+          <t>2403-24-24</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.62</v>
+        <v>2.75</v>
       </c>
       <c r="C31" t="n">
-        <v>0.57735</v>
+        <v>1.1547</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>0.375</v>
+        <v>0.9375</v>
       </c>
       <c r="F31" t="n">
-        <v>0.094</v>
+        <v>0.125</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2837</v>
+        <v>0.5454</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3295</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0984</v>
+        <v>0.1298</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1546</v>
+        <v>0.2482</v>
       </c>
       <c r="K31" t="n">
         <v>60</v>
@@ -5037,79 +5047,79 @@
         <v>37</v>
       </c>
       <c r="M31" t="n">
-        <v>0.75</v>
+        <v>1.875</v>
       </c>
       <c r="N31" t="n">
-        <v>0.0625</v>
+        <v>0.08333</v>
       </c>
       <c r="O31" t="n">
-        <v>0.5367</v>
+        <v>0.9234</v>
       </c>
       <c r="P31" t="n">
-        <v>0.03383</v>
+        <v>0.04511</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.01562</v>
+        <v>0.02083</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0625</v>
+        <v>0.08333</v>
       </c>
       <c r="S31" t="n">
-        <v>0.375</v>
+        <v>0.9375</v>
       </c>
       <c r="T31" t="n">
-        <v>0.094</v>
+        <v>0.125</v>
       </c>
       <c r="U31" t="n">
-        <v>0.2837</v>
+        <v>0.5454</v>
       </c>
       <c r="V31" t="n">
-        <v>0.3295</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="W31" t="n">
-        <v>0.0984</v>
+        <v>0.1298</v>
       </c>
       <c r="X31" t="n">
-        <v>0.1546</v>
+        <v>0.2482</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.75</v>
+        <v>1.875</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.0625</v>
+        <v>0.08333</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.5367</v>
+        <v>0.9234</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.03383</v>
+        <v>0.04511</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.01562</v>
+        <v>0.02083</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.0625</v>
+        <v>0.08333</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.39</v>
+        <v>1.31</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.375</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.39</v>
+        <v>1.31</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.375</v>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>2403-LH-08-08</t>
+          <t>2403-24-24</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>Male Union Large Hex, 3/4-16 x 3/4-16</t>
+          <t>Male Union, 1 7/8-12 x 1 7/8-12</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -5119,62 +5129,67 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>3/4-16</t>
+          <t>1 7/8-12</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>3/4-16</t>
+          <t>1 7/8-12</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Air-Way s63 only (double-pass 16 rows); JIC male end axials VERIFIED lib-wide (MS33656J); large-hex variant of 2403 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled; 2403-LH = the LARGE-HEX union (OMi "Straight-Large Hex", Air-Way s63, review table DesignTable_2403LH.xlsx), folded into the 2403 master as rows of the same shape: same JIC ends per dash, L1 and bores D1 / D2 from the 2403-LH table, hex = its C2 (as the legacy 2403 builder already did, 2026-09-06)</t>
+          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way ==MS51501 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>MS51501 L1/hex/bore AGREE</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>2403-LH-08-08</t>
+          <t>2403-24-24</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2403-LH-10-10</t>
+          <t>2403-32-24</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.88</v>
+        <v>3.15</v>
       </c>
       <c r="C32" t="n">
-        <v>0.65241</v>
+        <v>1.51843</v>
       </c>
       <c r="D32" t="n">
-        <v>1.13</v>
+        <v>2.63</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4375</v>
+        <v>1.25</v>
       </c>
       <c r="F32" t="n">
-        <v>0.107</v>
+        <v>0.125</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3553</v>
+        <v>0.7124</v>
       </c>
       <c r="H32" t="n">
-        <v>0.386</v>
+        <v>1.19</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1114</v>
+        <v>0.1292</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1546</v>
+        <v>0.3318</v>
       </c>
       <c r="K32" t="n">
         <v>60</v>
@@ -5183,79 +5198,79 @@
         <v>37</v>
       </c>
       <c r="M32" t="n">
-        <v>0.875</v>
+        <v>2.5</v>
       </c>
       <c r="N32" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.08333</v>
       </c>
       <c r="O32" t="n">
-        <v>0.6213</v>
+        <v>1.1734</v>
       </c>
       <c r="P32" t="n">
-        <v>0.03866</v>
+        <v>0.04511</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.01786</v>
+        <v>0.02083</v>
       </c>
       <c r="R32" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.08333</v>
       </c>
       <c r="S32" t="n">
-        <v>0.4375</v>
+        <v>0.9375</v>
       </c>
       <c r="T32" t="n">
-        <v>0.107</v>
+        <v>0.125</v>
       </c>
       <c r="U32" t="n">
-        <v>0.3553</v>
+        <v>0.5454</v>
       </c>
       <c r="V32" t="n">
-        <v>0.386</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>0.1114</v>
+        <v>0.1298</v>
       </c>
       <c r="X32" t="n">
-        <v>0.1546</v>
+        <v>0.2482</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.875</v>
+        <v>1.875</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.08333</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.6213</v>
+        <v>0.9234</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.03866</v>
+        <v>0.04511</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.01786</v>
+        <v>0.02083</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.08333</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.48</v>
+        <v>1.78</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.48</v>
+        <v>1.31</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.45</v>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>2403-LH-10-10</t>
+          <t>2403-32-24</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>Male Union Large Hex, 7/8-14 x 7/8-14</t>
+          <t>Male Union, 2 1/2-12 x 1 7/8-12</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -5265,12 +5280,12 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>7/8-14</t>
+          <t>2 1/2-12</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>7/8-14</t>
+          <t>1 7/8-12</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
@@ -5280,47 +5295,52 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Air-Way s63 only (double-pass 16 rows); JIC male end axials VERIFIED lib-wide (MS33656J); large-hex variant of 2403 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled; 2403-LH = the LARGE-HEX union (OMi "Straight-Large Hex", Air-Way s63, review table DesignTable_2403LH.xlsx), folded into the 2403 master as rows of the same shape: same JIC ends per dash, L1 and bores D1 / D2 from the 2403-LH table, hex = its C2 (as the legacy 2403 builder already did, 2026-09-06)</t>
+          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>unequal bores - bore step location unsourced</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>2403-LH-10-10</t>
+          <t>2403-32-24</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2403-LH-12-12</t>
+          <t>2403-32-32</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.16</v>
+        <v>3.4</v>
       </c>
       <c r="C33" t="n">
-        <v>0.79674</v>
+        <v>1.51843</v>
       </c>
       <c r="D33" t="n">
-        <v>1.38</v>
+        <v>2.63</v>
       </c>
       <c r="E33" t="n">
-        <v>0.53125</v>
+        <v>1.25</v>
       </c>
       <c r="F33" t="n">
         <v>0.125</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3895</v>
+        <v>0.7124</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4715</v>
+        <v>1.19</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1299</v>
+        <v>0.1292</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1851</v>
+        <v>0.3318</v>
       </c>
       <c r="K33" t="n">
         <v>60</v>
@@ -5329,13 +5349,13 @@
         <v>37</v>
       </c>
       <c r="M33" t="n">
-        <v>1.0625</v>
+        <v>2.5</v>
       </c>
       <c r="N33" t="n">
         <v>0.08333</v>
       </c>
       <c r="O33" t="n">
-        <v>0.7045</v>
+        <v>1.1734</v>
       </c>
       <c r="P33" t="n">
         <v>0.04511</v>
@@ -5347,31 +5367,31 @@
         <v>0.08333</v>
       </c>
       <c r="S33" t="n">
-        <v>0.53125</v>
+        <v>1.25</v>
       </c>
       <c r="T33" t="n">
         <v>0.125</v>
       </c>
       <c r="U33" t="n">
-        <v>0.3895</v>
+        <v>0.7124</v>
       </c>
       <c r="V33" t="n">
-        <v>0.4715</v>
+        <v>1.19</v>
       </c>
       <c r="W33" t="n">
-        <v>0.1299</v>
+        <v>0.1292</v>
       </c>
       <c r="X33" t="n">
-        <v>0.1851</v>
+        <v>0.3318</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.0625</v>
+        <v>2.5</v>
       </c>
       <c r="Z33" t="n">
         <v>0.08333</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.7045</v>
+        <v>1.1734</v>
       </c>
       <c r="AB33" t="n">
         <v>0.04511</v>
@@ -5383,25 +5403,25 @@
         <v>0.08333</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.61</v>
+        <v>1.78</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.08</v>
+        <v>1.7</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.61</v>
+        <v>1.78</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.08</v>
+        <v>1.7</v>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>2403-LH-12-12</t>
+          <t>2403-32-32</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>Male Union Large Hex, 1 1/16-12 x 1 1/16-12</t>
+          <t>Male Union, 2 1/2-12 x 2 1/2-12</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -5411,62 +5431,67 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>1 1/16-12</t>
+          <t>2 1/2-12</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>1 1/16-12</t>
+          <t>2 1/2-12</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Air-Way s63 only (double-pass 16 rows); JIC male end axials VERIFIED lib-wide (MS33656J); large-hex variant of 2403 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled; 2403-LH = the LARGE-HEX union (OMi "Straight-Large Hex", Air-Way s63, review table DesignTable_2403LH.xlsx), folded into the 2403 master as rows of the same shape: same JIC ends per dash, L1 and bores D1 / D2 from the 2403-LH table, hex = its C2 (as the legacy 2403 builder already did, 2026-09-06)</t>
+          <t>JIC ends: MS33656J==Brennan fleet (VERIFIED per dash); L1/hex: Air-Way ==MS51501 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>MS51501 L1/hex/bore AGREE</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>2403-LH-12-12</t>
+          <t>2403-32-32</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2403-LH-16-16</t>
+          <t>2403-LH-04-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.25</v>
+        <v>1.37</v>
       </c>
       <c r="C34" t="n">
-        <v>0.94108</v>
+        <v>0.39837</v>
       </c>
       <c r="D34" t="n">
-        <v>1.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>0.65625</v>
+        <v>0.21875</v>
       </c>
       <c r="F34" t="n">
-        <v>0.125</v>
+        <v>0.075</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4365</v>
+        <v>0.2608</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5965</v>
+        <v>0.182</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1292</v>
+        <v>0.0795</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1858</v>
+        <v>0.1135</v>
       </c>
       <c r="K34" t="n">
         <v>60</v>
@@ -5475,79 +5500,79 @@
         <v>37</v>
       </c>
       <c r="M34" t="n">
-        <v>1.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="N34" t="n">
-        <v>0.08333</v>
+        <v>0.05</v>
       </c>
       <c r="O34" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.4538</v>
       </c>
       <c r="P34" t="n">
-        <v>0.04511</v>
+        <v>0.02706</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.02083</v>
+        <v>0.0125</v>
       </c>
       <c r="R34" t="n">
-        <v>0.08333</v>
+        <v>0.05</v>
       </c>
       <c r="S34" t="n">
-        <v>0.65625</v>
+        <v>0.21875</v>
       </c>
       <c r="T34" t="n">
-        <v>0.125</v>
+        <v>0.075</v>
       </c>
       <c r="U34" t="n">
-        <v>0.4365</v>
+        <v>0.2608</v>
       </c>
       <c r="V34" t="n">
-        <v>0.5965</v>
+        <v>0.182</v>
       </c>
       <c r="W34" t="n">
-        <v>0.1292</v>
+        <v>0.0795</v>
       </c>
       <c r="X34" t="n">
-        <v>0.1858</v>
+        <v>0.1135</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.3125</v>
+        <v>0.4375</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.08333</v>
+        <v>0.05</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.4538</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.04511</v>
+        <v>0.02706</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.02083</v>
+        <v>0.0125</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.08333</v>
+        <v>0.05</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.84</v>
+        <v>0.17</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.125</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.84</v>
+        <v>0.17</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.125</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>2403-LH-16-16</t>
+          <t>2403-LH-04-04</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>Male Union Large Hex, 1 5/16-12 x 1 5/16-12</t>
+          <t>Male Union Large Hex, 7/16-20 x 7/16-20</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -5557,12 +5582,12 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>1 5/16-12</t>
+          <t>7/16-20</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>1 5/16-12</t>
+          <t>7/16-20</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
@@ -5577,42 +5602,42 @@
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>2403-LH-16-16</t>
+          <t>2403-LH-04-04</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2403-LH-20-20</t>
+          <t>2403-LH-06-06</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.43</v>
+        <v>1.41</v>
       </c>
       <c r="C35" t="n">
-        <v>1.08542</v>
+        <v>0.46765</v>
       </c>
       <c r="D35" t="n">
-        <v>1.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8125</v>
+        <v>0.28125</v>
       </c>
       <c r="F35" t="n">
-        <v>0.125</v>
+        <v>0.083</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4316</v>
+        <v>0.2515</v>
       </c>
       <c r="H35" t="n">
-        <v>0.753</v>
+        <v>0.2405</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1288</v>
+        <v>0.0898</v>
       </c>
       <c r="J35" t="n">
-        <v>0.2382</v>
+        <v>0.1082</v>
       </c>
       <c r="K35" t="n">
         <v>60</v>
@@ -5621,109 +5646,990 @@
         <v>37</v>
       </c>
       <c r="M35" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.1082</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>2403-LH-06-06</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>Male Union Large Hex, 9/16-18 x 9/16-18</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>2403</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>9/16-18</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>9/16-18</t>
+        </is>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Air-Way s63 only (double-pass 16 rows); JIC male end axials VERIFIED lib-wide (MS33656J); large-hex variant of 2403 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled; 2403-LH = the LARGE-HEX union (OMi "Straight-Large Hex", Air-Way s63, review table DesignTable_2403LH.xlsx), folded into the 2403 master as rows of the same shape: same JIC ends per dash, L1 and bores D1 / D2 from the 2403-LH table, hex = its C2 (as the legacy 2403 builder already did, 2026-09-06)</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>2403-LH-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2403-LH-08-08</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.57735</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="K36" t="n">
+        <v>60</v>
+      </c>
+      <c r="L36" t="n">
+        <v>37</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.5367</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.5367</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>2403-LH-08-08</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>Male Union Large Hex, 3/4-16 x 3/4-16</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>2403</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>3/4-16</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>3/4-16</t>
+        </is>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Air-Way s63 only (double-pass 16 rows); JIC male end axials VERIFIED lib-wide (MS33656J); large-hex variant of 2403 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled; 2403-LH = the LARGE-HEX union (OMi "Straight-Large Hex", Air-Way s63, review table DesignTable_2403LH.xlsx), folded into the 2403 master as rows of the same shape: same JIC ends per dash, L1 and bores D1 / D2 from the 2403-LH table, hex = its C2 (as the legacy 2403 builder already did, 2026-09-06)</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>2403-LH-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2403-LH-10-10</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.65241</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.1114</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="K37" t="n">
+        <v>60</v>
+      </c>
+      <c r="L37" t="n">
+        <v>37</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.6213</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.1114</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.6213</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>2403-LH-10-10</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>Male Union Large Hex, 7/8-14 x 7/8-14</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>2403</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>7/8-14</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>7/8-14</t>
+        </is>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Air-Way s63 only (double-pass 16 rows); JIC male end axials VERIFIED lib-wide (MS33656J); large-hex variant of 2403 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled; 2403-LH = the LARGE-HEX union (OMi "Straight-Large Hex", Air-Way s63, review table DesignTable_2403LH.xlsx), folded into the 2403 master as rows of the same shape: same JIC ends per dash, L1 and bores D1 / D2 from the 2403-LH table, hex = its C2 (as the legacy 2403 builder already did, 2026-09-06)</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>2403-LH-10-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2403-LH-12-12</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.79674</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="K38" t="n">
+        <v>60</v>
+      </c>
+      <c r="L38" t="n">
+        <v>37</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.7045</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.7045</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>2403-LH-12-12</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>Male Union Large Hex, 1 1/16-12 x 1 1/16-12</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>2403</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>1 1/16-12</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>1 1/16-12</t>
+        </is>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Air-Way s63 only (double-pass 16 rows); JIC male end axials VERIFIED lib-wide (MS33656J); large-hex variant of 2403 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled; 2403-LH = the LARGE-HEX union (OMi "Straight-Large Hex", Air-Way s63, review table DesignTable_2403LH.xlsx), folded into the 2403 master as rows of the same shape: same JIC ends per dash, L1 and bores D1 / D2 from the 2403-LH table, hex = its C2 (as the legacy 2403 builder already did, 2026-09-06)</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>2403-LH-12-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2403-LH-16-16</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.94108</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="K39" t="n">
+        <v>60</v>
+      </c>
+      <c r="L39" t="n">
+        <v>37</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.7514999999999999</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.7514999999999999</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>2403-LH-16-16</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>Male Union Large Hex, 1 5/16-12 x 1 5/16-12</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>2403</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>1 5/16-12</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>1 5/16-12</t>
+        </is>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Air-Way s63 only (double-pass 16 rows); JIC male end axials VERIFIED lib-wide (MS33656J); large-hex variant of 2403 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled; 2403-LH = the LARGE-HEX union (OMi "Straight-Large Hex", Air-Way s63, review table DesignTable_2403LH.xlsx), folded into the 2403 master as rows of the same shape: same JIC ends per dash, L1 and bores D1 / D2 from the 2403-LH table, hex = its C2 (as the legacy 2403 builder already did, 2026-09-06)</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>2403-LH-16-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2403-LH-20-20</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1.08542</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="K40" t="n">
+        <v>60</v>
+      </c>
+      <c r="L40" t="n">
+        <v>37</v>
+      </c>
+      <c r="M40" t="n">
         <v>1.625</v>
       </c>
-      <c r="N35" t="n">
-        <v>0.08333</v>
-      </c>
-      <c r="O35" t="n">
+      <c r="N40" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O40" t="n">
         <v>0.7986</v>
       </c>
-      <c r="P35" t="n">
+      <c r="P40" t="n">
         <v>0.04511</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Q40" t="n">
         <v>0.02083</v>
       </c>
-      <c r="R35" t="n">
-        <v>0.08333</v>
-      </c>
-      <c r="S35" t="n">
+      <c r="R40" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S40" t="n">
         <v>0.8125</v>
       </c>
-      <c r="T35" t="n">
+      <c r="T40" t="n">
         <v>0.125</v>
       </c>
-      <c r="U35" t="n">
+      <c r="U40" t="n">
         <v>0.4316</v>
       </c>
-      <c r="V35" t="n">
+      <c r="V40" t="n">
         <v>0.753</v>
       </c>
-      <c r="W35" t="n">
+      <c r="W40" t="n">
         <v>0.1288</v>
       </c>
-      <c r="X35" t="n">
+      <c r="X40" t="n">
         <v>0.2382</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="Y40" t="n">
         <v>1.625</v>
       </c>
-      <c r="Z35" t="n">
-        <v>0.08333</v>
-      </c>
-      <c r="AA35" t="n">
+      <c r="Z40" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AA40" t="n">
         <v>0.7986</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AB40" t="n">
         <v>0.04511</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AC40" t="n">
         <v>0.02083</v>
       </c>
-      <c r="AD35" t="n">
-        <v>0.08333</v>
-      </c>
-      <c r="AE35" t="n">
+      <c r="AD40" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AE40" t="n">
         <v>1.08</v>
       </c>
-      <c r="AF35" t="n">
+      <c r="AF40" t="n">
         <v>1.215</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AG40" t="n">
         <v>1.08</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AH40" t="n">
         <v>1.215</v>
       </c>
-      <c r="AI35" t="inlineStr">
+      <c r="AI40" t="inlineStr">
         <is>
           <t>2403-LH-20-20</t>
         </is>
       </c>
-      <c r="AJ35" t="inlineStr">
+      <c r="AJ40" t="inlineStr">
         <is>
           <t>Male Union Large Hex, 1 5/8-12 x 1 5/8-12</t>
         </is>
       </c>
-      <c r="AK35" t="inlineStr">
+      <c r="AK40" t="inlineStr">
         <is>
           <t>2403</t>
         </is>
       </c>
-      <c r="AL35" t="inlineStr">
+      <c r="AL40" t="inlineStr">
         <is>
           <t>1 5/8-12</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
+      <c r="AM40" t="inlineStr">
         <is>
           <t>1 5/8-12</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
+      <c r="AN40" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AO35" t="inlineStr">
+      <c r="AO40" t="inlineStr">
         <is>
           <t>Air-Way s63 only (double-pass 16 rows); JIC male end axials VERIFIED lib-wide (MS33656J); large-hex variant of 2403 | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled; 2403-LH = the LARGE-HEX union (OMi "Straight-Large Hex", Air-Way s63, review table DesignTable_2403LH.xlsx), folded into the 2403 master as rows of the same shape: same JIC ends per dash, L1 and bores D1 / D2 from the 2403-LH table, hex = its C2 (as the legacy 2403 builder already did, 2026-09-06)</t>
         </is>
       </c>
-      <c r="AQ35" t="inlineStr">
+      <c r="AQ40" t="inlineStr">
         <is>
           <t>2403-LH-20-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2403-LH-24-24</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.22687</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="K41" t="n">
+        <v>60</v>
+      </c>
+      <c r="L41" t="n">
+        <v>37</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.9234</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.9234</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>2403-LH-24-24</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>Male Union Large Hex, 1 7/8-12 x 1 7/8-12</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>2403</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>1 7/8-12</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>1 7/8-12</t>
+        </is>
+      </c>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L1@DRIVE: Brennan TFA catalog p5 table TFA-p005-t02 "2403-LH MJ-MJ STRAIGHT LARGE HEX" row 2403-LH-24-24 col "L LGTH" = "2.75" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 575.7, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p5 2403-LH drawing: L = overall, C HEX = the large body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 16/16 rows with an Air-Way/OMi value agree with this catalog column to rounding; C2HEX@HEX: Brennan TFA catalog p5 table TFA-p005-t02 "2403-LH MJ-MJ STRAIGHT LARGE HEX" row 2403-LH-24-24 col "C HEX" = "2.125" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 575.7, page verified) [Brennan = yes 2026-10-18] - large body hex; mapping: TFA p5 2403-LH drawing: L = overall, C HEX = the large body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 16/16 rows with an Air-Way/OMi value agree with this catalog column to rounding; D1@BORE: Brennan TFA catalog p5 table TFA-p005-t02 "2403-LH MJ-MJ STRAIGHT LARGE HEX" row 2403-LH-24-24 col "B1 DRILL" = "1.312" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 575.7, page verified) [Brennan = yes 2026-10-18] - bore end B1; mapping: TFA p5 2403-LH drawing: L = overall, C HEX = the large body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 16/16 rows with an Air-Way/OMi value agree with this catalog column to rounding; D2@BORE: Brennan TFA catalog p5 table TFA-p005-t02 "2403-LH MJ-MJ STRAIGHT LARGE HEX" row 2403-LH-24-24 col "B2 DRILL" = "1.312" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 575.7, page verified) [Brennan = yes 2026-10-18] - bore end B2; mapping: TFA p5 2403-LH drawing: L = overall, C HEX = the large body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 16/16 rows with an Air-Way/OMi value agree with this catalog column to rounding; THDMAJ_B1@DRIVE: end library gen_straight2 JIC[24] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major (1 7/8-12); THDMAJ_B2@DRIVE: end library gen_straight2 JIC[24] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major (1 7/8-12); $PRP@Threads: end library gen_straight2 JIC[24] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread texts, format of the built 2403LH rows | MODEL: JIC ends A and B: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L1 / hex / bores D1, D2: review table (Air-Way; matched-dash rows == MS51501D); hex over the whole length between the two JIC ends (legacy 2403 builder); bore step D1/D2 at the hex mid-plane (ASSUMPTION - unsourced, same rule as the legacy 2403 builder and 6400; no effect where D1 = D2); hex end chamfers NOT modelled; 2403-LH = the LARGE-HEX union (OMi "Straight-Large Hex", Air-Way s63, review table DesignTable_2403LH.xlsx), folded into the 2403 master as rows of the same shape: same JIC ends per dash, L1 and bores D1 / D2 from the 2403-LH table, hex = its C2 (as the legacy 2403 builder already did, 2026-09-06)</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L1 / large hex / bores from the Brennan TFA catalog p5 alone; JIC ends from the 2403 end library (load_2403 fold)</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>2403-LH-24-24</t>
         </is>
       </c>
     </row>
